--- a/data/county_inputs.xlsx
+++ b/data/county_inputs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GeorgiaTechMaterial\6thSemester-Fall2026\Practical_Practicum\Code\lagom_track_a_module1_python_project\lagom_fiscal_impact_model_module1\lagom_fiscal_impact_model\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GeorgiaTechMaterial\6thSemester-Fall2026\Practical_Practicum\Code\lagom_fiscal_impact_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E052F886-ED04-4460-9699-3E1FABA5BDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5948D647-3EB1-49F7-A33A-12A42B423239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>County</t>
   </si>
@@ -103,6 +103,15 @@
   </si>
   <si>
     <t>Kansas</t>
+  </si>
+  <si>
+    <t>School District</t>
+  </si>
+  <si>
+    <t>Wichita</t>
+  </si>
+  <si>
+    <t>District Capacity</t>
   </si>
 </sst>
 </file>
@@ -161,12 +170,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,27 +515,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="19.6328125" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="18.81640625" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" customWidth="1"/>
-    <col min="11" max="11" width="28.90625" customWidth="1"/>
-    <col min="12" max="12" width="23.7265625" customWidth="1"/>
-    <col min="13" max="16" width="28.90625" customWidth="1"/>
-    <col min="17" max="17" width="27.36328125" customWidth="1"/>
-    <col min="18" max="18" width="34.08984375" customWidth="1"/>
-    <col min="19" max="19" width="27.453125" customWidth="1"/>
-    <col min="20" max="20" width="32.7265625" customWidth="1"/>
-    <col min="21" max="21" width="21.6328125" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="19.6328125" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" customWidth="1"/>
+    <col min="8" max="8" width="18.26953125" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" customWidth="1"/>
+    <col min="12" max="12" width="28.90625" customWidth="1"/>
+    <col min="13" max="13" width="23.7265625" customWidth="1"/>
+    <col min="14" max="18" width="28.90625" customWidth="1"/>
+    <col min="19" max="19" width="27.36328125" customWidth="1"/>
+    <col min="20" max="20" width="34.08984375" customWidth="1"/>
+    <col min="21" max="21" width="27.453125" customWidth="1"/>
+    <col min="22" max="22" width="32.7265625" customWidth="1"/>
+    <col min="23" max="23" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,119 +544,131 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
         <v>150</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>223000</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.115</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>27.567</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>16.754000000000001</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>51.402000000000001</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>32.340000000000003</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>0.01</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>0</v>
       </c>
-      <c r="O2" s="2">
+      <c r="P2" s="2">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="P2" s="2">
+      <c r="Q2" s="2">
         <v>1.18E-2</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="3">
+        <v>60000</v>
+      </c>
+      <c r="T2" t="s">
         <v>18</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>19</v>
       </c>
     </row>
